--- a/Simulation/Results/p.rand_Ten.Fixed.Ints_mean.surv.30.xlsx
+++ b/Simulation/Results/p.rand_Ten.Fixed.Ints_mean.surv.30.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">rand</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2 hours</t>
+    <t xml:space="preserve">5.4 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 hours</t>
   </si>
 </sst>
 </file>
@@ -419,13 +419,13 @@
         <v>50</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0528</v>
+        <v>0.0505</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0561</v>
+        <v>0.0524</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0543</v>
+        <v>0.0523</v>
       </c>
       <c r="E2" t="n">
         <v>0.0333333333333333</v>
@@ -448,13 +448,13 @@
         <v>100</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0502</v>
+        <v>0.0496</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0504</v>
+        <v>0.048</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0478</v>
+        <v>0.0454</v>
       </c>
       <c r="E3" t="n">
         <v>0.0333333333333333</v>
@@ -477,13 +477,13 @@
         <v>200</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0512</v>
+        <v>0.0506</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0556</v>
+        <v>0.0539</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0533</v>
+        <v>0.0528</v>
       </c>
       <c r="E4" t="n">
         <v>0.0333333333333333</v>
@@ -506,13 +506,13 @@
         <v>500</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0474</v>
+        <v>0.047</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0487</v>
+        <v>0.0478</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0499</v>
+        <v>0.0503</v>
       </c>
       <c r="E5" t="n">
         <v>0.0333333333333333</v>
